--- a/MikroTik_PoC_Enforcement_Tracker.xlsx
+++ b/MikroTik_PoC_Enforcement_Tracker.xlsx
@@ -4774,9 +4774,9 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>[02-A]</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>[03]</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>ALLOW ICMP (PING) FOR POC VERIFICATION</t>
+          <t>ALLOW ICMP (PING) FOR VERIFICATION</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -4816,9 +4816,9 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>[02-B]</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>[03-A]</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -4838,64 +4838,64 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>80,443</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>dst: waf-frontend</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>ALLOW PUBLIC WEB TRAFFIC TO WAF</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>All Subnets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>[03-B]</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>accept</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>8881</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>src: 10.27.101.41 -&gt; dst: 10.27.101.165</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>ALLOW WAF TO BACKEND APACHE</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>PoC Targets</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>[03]</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>forward</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>accept</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>tcp</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>80,443</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>dst: waf-frontend</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>ALLOW PUBLIC WEB TRAFFIC TO WAF</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>All Subnets</t>
         </is>
       </c>
     </row>
